--- a/docs/hoang-huy-phat/sosach2024/BAO_CAO_CONG_NO_HHP_2024.xlsx
+++ b/docs/hoang-huy-phat/sosach2024/BAO_CAO_CONG_NO_HHP_2024.xlsx
@@ -10698,7 +10698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D244"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10828,3793 +10828,721 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thu phi BDSD 01/2024, So TK: 110649896789, SDT: 09</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>848941</v>
       </c>
       <c r="C8" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-18000</v>
+        <v>848941</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CTY Hoang Huy Phat TT tien hang</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1481058219</v>
       </c>
       <c r="C9" t="n">
-        <v>2526848202</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-2526848202</v>
+        <v>1481058219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>848941</v>
+        <v>8999302776</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>848941</v>
+        <v>8999302776</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1481058219</v>
+        <v>26090095052</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1481058219</v>
+        <v>26090095052</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8999302776</v>
+        <v>13297944100</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>8999302776</v>
+        <v>13297944100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
+          <t>CÔNG TY TNHH MTV THƯƠNG MẠI &amp; DỊCH VỤ ẮC QUY DIỆN LIÊN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26090095052</v>
+        <v>5800000</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>26090095052</v>
+        <v>5800000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Don hang Hoang Huy Phat A</t>
+          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>30886907099</v>
       </c>
       <c r="C14" t="n">
-        <v>155125356</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-155125356</v>
+        <v>30886907099</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ÂN PHÚ KON TUM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13297944100</v>
+        <v>21910839</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>13297944100</v>
+        <v>21910839</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV THƯƠNG MẠI &amp; DỊCH VỤ ẮC QUY DIỆN LIÊN</t>
+          <t>Công ty TNHH Thuần Lý</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5800000</v>
+        <v>47850003</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5800000</v>
+        <v>47850003</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CTY Hoang Huy Phat Thanh toan tien hang</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>10259370</v>
       </c>
       <c r="C17" t="n">
-        <v>206423089</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-206423089</v>
+        <v>10259370</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>682000</v>
       </c>
       <c r="C18" t="n">
-        <v>360000</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-360000</v>
+        <v>682000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Thu phi duy tri dich vu IB 01/2024</t>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1661000</v>
       </c>
       <c r="C19" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-35000</v>
+        <v>1661000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
+          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30886907099</v>
+        <v>9394000</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>30886907099</v>
+        <v>9394000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ÂN PHÚ KON TUM</t>
+          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21910839</v>
+        <v>590494939</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>21910839</v>
+        <v>590494939</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thuần Lý</t>
+          <t>TỔNG CÔNG TY HÀNG KHÔNG VIỆT NAM  - CTCP</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>47850003</v>
+        <v>2195000</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>47850003</v>
+        <v>2195000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>Công ty cổ phần MISA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10259370</v>
+        <v>16852500</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>10259370</v>
+        <v>16852500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CONG TY HOANG HUY PHAT THANH TOAN TIEN HANG</t>
+          <t>CÔNG TY TNHH ĐĂNG KIỂM CAO NGUYÊN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2277818</v>
       </c>
       <c r="C24" t="n">
-        <v>578000</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-578000</v>
+        <v>2277818</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI DỊCH VỤ TỔNG HỢP XUÂN TÙNG</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>682000</v>
+        <v>324000</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>682000</v>
+        <v>324000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TRA TIEN HANG</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MAY THÊU GIÀY AN PHƯỚC TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>5166000</v>
       </c>
       <c r="C26" t="n">
-        <v>57906</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-57906</v>
+        <v>5166000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
+          <t>CHI NHÁNH CÔNG TY TNHH DKSH VIỆT NAM TẠI THÀNH PHỐ ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1661000</v>
+        <v>3398271030</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1661000</v>
+        <v>3398271030</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HHP THANH TOAN TIEN HANG</t>
+          <t>CHI NHÁNH CÔNG TY TNHH TRUYỀN HÌNH CÁP SAIGONTOURIST-TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2070000</v>
       </c>
       <c r="C28" t="n">
-        <v>53987</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-53987</v>
+        <v>2070000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN PCCC NGỌC MINH</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9394000</v>
+        <v>99712500</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>9394000</v>
+        <v>99712500</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
+          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>590494939</v>
+        <v>6489481</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>590494939</v>
+        <v>6489481</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Thu phi BDSD 02/2024, So TK: 110649896789, SDT: 09</t>
+          <t>CÔNG TY CỔ PHẦN ĐIỆN TỬ VIỄN THÔNG ÁNH DƯƠNG</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>6490000</v>
       </c>
       <c r="C31" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-18000</v>
+        <v>6490000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CTY HOANG HUY PHAT TT TIEN HANG HHP A</t>
+          <t>CÔNG TY TNHH FONTERRA BRANDS (VIỆT NAM)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>56146</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-56146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TỔNG CÔNG TY HÀNG KHÔNG VIỆT NAM  - CTCP</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2195000</v>
+        <v>7127600</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2195000</v>
+        <v>7127600</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CONG TY TNHH MTV HOANG HUY PHAT TT TIEN DON HANG H</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>7900000</v>
       </c>
       <c r="C34" t="n">
-        <v>80722</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-80722</v>
+        <v>7900000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Thu phi duy tri dich vu IB 02/2024</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI HƯNG PHÁT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="C35" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-35000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Công ty cổ phần MISA</t>
+          <t>CÔNG TY CỔ PHẦN BỆNH VIỆN ĐẠI HỌC Y DƯỢC - HOÀNG ANH GIA LAI</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16852500</v>
+        <v>1488000</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>16852500</v>
+        <v>1488000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CTY HOANG HUY PHAT THANH TOAN TIEN HANG</t>
+          <t>DOANH NGHIỆP TƯ NHÂN MINH LỘC TIẾN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>14551680</v>
       </c>
       <c r="C37" t="n">
-        <v>766439240</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>-766439240</v>
+        <v>14551680</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>THANH TOAN TIEN HANG (HHP B)</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN AN PHÁT LỘC GIA LAI</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>3749000</v>
       </c>
       <c r="C38" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-11000</v>
+        <v>3749000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>THANH TOAN TIEN HANG (H4P A)</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>3651067</v>
       </c>
       <c r="C39" t="n">
-        <v>30520</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>-30520</v>
+        <v>3651067</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>THANH TOAN TIEN HANG</t>
+          <t>CHI NHÁNH CÔNG TY CP XĂNG DẦU DẦU KHÍ PV OIL MIỀN TRUNG TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1338350</v>
       </c>
       <c r="C40" t="n">
-        <v>160931</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-160931</v>
+        <v>1338350</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Thu phi BDSD 03/2024, So TK: 110649896789, SDT: 09</t>
+          <t>CÔNG TY TNHH SHOPEE</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1300522</v>
       </c>
       <c r="C41" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>-18000</v>
+        <v>1300522</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CTY HOANG HUY PHAT TT tien hang</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN IN PHOTOCOPY LAM SƠN</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>626000</v>
       </c>
       <c r="C42" t="n">
-        <v>617614164</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-617614164</v>
+        <v>626000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CTY HOANG HUY PHAT TT tien hang HHP B</t>
+          <t>CHI NHÁNH CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI VÀ DỊCH VỤ HNI TẠI IA GRAI</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>3100000</v>
       </c>
       <c r="C43" t="n">
-        <v>17023023</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-17023023</v>
+        <v>3100000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CTY Hoang Huy Phat TT tien hang HHP A</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>17154000</v>
       </c>
       <c r="C44" t="n">
-        <v>13947018</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-13947018</v>
+        <v>17154000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐĂNG KIỂM CAO NGUYÊN</t>
+          <t>CÔNG TY TNHH DG GROUP</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2277818</v>
+        <v>935710</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2277818</v>
+        <v>935710</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Thu phi duy tri dich vu IB 03/2024</t>
+          <t>CÔNG TY CỔ PHẦN CẤP THOÁT NƯỚC GIA LAI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>214950</v>
       </c>
       <c r="C46" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>-35000</v>
+        <v>214950</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI DỊCH VỤ TỔNG HỢP XUÂN TÙNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HUY VŨ</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>324000</v>
+        <v>2700000</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>324000</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>So GD: 500A24315Z9M47ZJ TRA TIEN HANG</t>
+          <t>CÔNG TY CỔ PHẦN VIỆT ĐÔNG DƯƠNG</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>24080000</v>
       </c>
       <c r="C48" t="n">
-        <v>58247</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>-58247</v>
+        <v>24080000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MAY THÊU GIÀY AN PHƯỚC TẠI GIA LAI</t>
+          <t>CÔNG TY TNHH BẾN THUYỀN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5166000</v>
+        <v>1198000</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>5166000</v>
+        <v>1198000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CONG TY HHP THANH TOAN TIEN HANG</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY THƯƠNG MẠI KỸ THUẬT VÀ ĐẦU TƯ - CÔNG TY CỔ PHẦN TẠI TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="C50" t="n">
-        <v>20154</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-20154</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HHP A</t>
+          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>46454752</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>-46454752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH DKSH VIỆT NAM TẠI THÀNH PHỐ ĐÀ NẴNG</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3398271030</v>
+        <v>4474840</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>3398271030</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="n">
-        <v>972419</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-972419</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH TRUYỀN HÌNH CÁP SAIGONTOURIST-TỈNH GIA LAI</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>2070000</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2070000</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 04/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-18000</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 805005977392,  So tien goc: 58,</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" t="n">
-        <v>74874586</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-74874586</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 804005985536,  So tien goc: 49,</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" t="n">
-        <v>51174865</v>
-      </c>
-      <c r="D57" t="n">
-        <v>-51174865</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN PCCC NGỌC MINH</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>99712500</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>99712500</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>6489481</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>6489481</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐIỆN TỬ VIỄN THÔNG ÁNH DƯƠNG</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>6490000</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>6490000</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 803005988944,  So tien goc: 70,</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" t="n">
-        <v>70929054</v>
-      </c>
-      <c r="D61" t="n">
-        <v>-70929054</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH FONTERRA BRANDS (VIỆT NAM)</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 04/2024</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 05/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-18000</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>HD 1429</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" t="n">
-        <v>4526182</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-4526182</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 05/2024</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>7127600</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="n">
-        <v>7127600</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 805006194221,  So tien goc: 13,</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" t="n">
-        <v>13791716</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-13791716</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 06/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" t="n">
-        <v>18000</v>
-      </c>
-      <c r="D69" t="n">
-        <v>-18000</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ ĐỨC THANH GIA LAI</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>7900000</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI HƯNG PHÁT</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>CT DI:415718311165 Luan chuyen sang TK VCB Cty</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" t="n">
-        <v>23022000</v>
-      </c>
-      <c r="D72" t="n">
-        <v>-23022000</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN BỆNH VIỆN ĐẠI HỌC Y DƯỢC - HOÀNG ANH GIA LAI</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1488000</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1488000</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 06/2024</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D74" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 804006198600,  So tien goc: 316</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" t="n">
-        <v>317750778</v>
-      </c>
-      <c r="D75" t="n">
-        <v>-317750778</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>TT tien hang CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" t="n">
-        <v>130173760</v>
-      </c>
-      <c r="D76" t="n">
-        <v>-130173760</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>TT tien hang CTY CLM B</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" t="n">
-        <v>62787749</v>
-      </c>
-      <c r="D77" t="n">
-        <v>-62787749</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>CTY HHP Thanh toan tien hang</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" t="n">
-        <v>58948684</v>
-      </c>
-      <c r="D78" t="n">
-        <v>-58948684</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>So GD: 500A2461433SK8SH Cong Ty Hoang Huy Phat tha</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" t="n">
-        <v>293391157</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-293391157</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>So GD: 500A24614337YW2D CTY TNHH MTV Hoang Huy Pha</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" t="n">
-        <v>221460525</v>
-      </c>
-      <c r="D80" t="n">
-        <v>-221460525</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 806006201571,  So tien goc: 72,</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" t="n">
-        <v>74300196</v>
-      </c>
-      <c r="D81" t="n">
-        <v>-74300196</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG (HHP 4)</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" t="n">
-        <v>37556</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-37556</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG (HHP B)</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" t="n">
-        <v>11095</v>
-      </c>
-      <c r="D83" t="n">
-        <v>-11095</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>DOANH NGHIỆP TƯ NHÂN MINH LỘC TIẾN</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>14551680</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="n">
-        <v>14551680</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 07/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>CTY Hoang Huy Phat thanh toan tien mua dau nhot</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" t="n">
-        <v>14551680</v>
-      </c>
-      <c r="D86" t="n">
-        <v>-14551680</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>CTy Hoang Huy Phat TT tien hang</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" t="n">
-        <v>100958574</v>
-      </c>
-      <c r="D87" t="n">
-        <v>-100958574</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Cty Hoang Huy Phat TT tien hang</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" t="n">
-        <v>330381472</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-330381472</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>So GD: 500A2470BR2HMBWN TT TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" t="n">
-        <v>59824</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-59824</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG (HHPB)</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" t="n">
-        <v>25115</v>
-      </c>
-      <c r="D90" t="n">
-        <v>-25115</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG (HHPA)</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" t="n">
-        <v>43976</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-43976</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>HOANG HUY PHAT CHI LUONG THANG 06/2024</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" t="n">
-        <v>162634632</v>
-      </c>
-      <c r="D92" t="n">
-        <v>-162634632</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>So GD: 500A2470P8ULX5US CTY Hoang Huy Phat TT tien</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" t="n">
-        <v>48857644</v>
-      </c>
-      <c r="D93" t="n">
-        <v>-48857644</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>So GD: 500A2470P8U1GXMF CTY Hoang Huy Phat TT tien</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" t="n">
-        <v>193174762</v>
-      </c>
-      <c r="D94" t="n">
-        <v>-193174762</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 804006204721,  So tien goc: 195</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" t="n">
-        <v>199326358</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-199326358</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG HHPB</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" t="n">
-        <v>11000</v>
-      </c>
-      <c r="D96" t="n">
-        <v>-11000</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG HD 12952,12951,12950</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" t="n">
-        <v>14350</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-14350</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG HHPA (HD 33008+33007)</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" t="n">
-        <v>56618</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-56618</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 07/2024</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN AN PHÁT LỘC GIA LAI</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>3749000</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>3749000</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>3651067</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="n">
-        <v>3651067</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 807006210371,  So tien goc: 6,4</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" t="n">
-        <v>7686264</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-7686264</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>So GD: 500A24710SUBMYBP CTY HOANG HUY PHAT TT TIEN</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" t="n">
-        <v>165651728</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-165651728</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Dot 2</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" t="n">
-        <v>12819456</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-12819456</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Nop tien Bao Hiem T7/2024  dot 3</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" t="n">
-        <v>28452502</v>
-      </c>
-      <c r="D105" t="n">
-        <v>-28452502</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Dot 1</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" t="n">
-        <v>65092950</v>
-      </c>
-      <c r="D106" t="n">
-        <v>-65092950</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY CP XĂNG DẦU DẦU KHÍ PV OIL MIỀN TRUNG TẠI GIA LAI</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>1338350</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="n">
-        <v>1338350</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 08/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D108" t="n">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>CTY HOANG HUY PHAT TT TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" t="n">
-        <v>30116515</v>
-      </c>
-      <c r="D109" t="n">
-        <v>-30116515</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH SHOPEE</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>1300522</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" t="n">
-        <v>1300522</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>So GD: 500A24806V3YWAE0 CTY HOANG HUY PHAT TT tien</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" t="n">
-        <v>203627514</v>
-      </c>
-      <c r="D111" t="n">
-        <v>-203627514</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 805006221155,  So tien goc: 12,</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" t="n">
-        <v>12846459</v>
-      </c>
-      <c r="D112" t="n">
-        <v>-12846459</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>ung luong T7.24</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="D113" t="n">
-        <v>-4000000</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>DO HOP T1 +T5+T6.24</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" t="n">
-        <v>2380000</v>
-      </c>
-      <c r="D114" t="n">
-        <v>-2380000</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>thuong DNLM tu 01.04 den 14.06.24</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="D115" t="n">
-        <v>-12000000</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>LUONG T7.2024</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" t="n">
-        <v>264335036</v>
-      </c>
-      <c r="D116" t="n">
-        <v>-264335036</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>LUONG T7.24</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" t="n">
-        <v>34599724</v>
-      </c>
-      <c r="D117" t="n">
-        <v>-34599724</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>thuong DNLM tu 01.04 den 14.06</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
-      <c r="C118" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="D118" t="n">
-        <v>-8000000</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>DO HOP T5 VA T6.2024</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" t="n">
-        <v>421000</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-421000</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>So GD: 500A2480C01E7EFW Luan chuyen sang TK Vietco</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="D120" t="n">
-        <v>-23000000</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN IN PHOTOCOPY LAM SƠN</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>626000</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" t="n">
-        <v>626000</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG HOA DON SO 14801,14802,14803</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" t="n">
-        <v>18079</v>
-      </c>
-      <c r="D122" t="n">
-        <v>-18079</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>THANH TOAN TIEN HAANG HD SO: 15003,15004,15005 NGA</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" t="n">
-        <v>11267</v>
-      </c>
-      <c r="D123" t="n">
-        <v>-11267</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">So GD: 500A2480MPBV9996 CTY HOANG HUP PHAT chuyen </t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" t="n">
-        <v>687700</v>
-      </c>
-      <c r="D124" t="n">
-        <v>-687700</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>35,785,549 VND,  So tien tra lai phat: 0 VND,  Phi tra no truoc han: 0 VND</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" t="n">
-        <v>69860050</v>
-      </c>
-      <c r="D125" t="n">
-        <v>-69860050</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 805006237533,  So tien goc: 594</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" t="n">
-        <v>595362028</v>
-      </c>
-      <c r="D126" t="n">
-        <v>-595362028</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI VÀ DỊCH VỤ HNI TẠI IA GRAI</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="C127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" t="n">
-        <v>3100000</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 08/2024</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D128" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG HHP B</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" t="n">
-        <v>11000</v>
-      </c>
-      <c r="D129" t="n">
-        <v>-11000</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>UNG LUONG T8/24</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-4000000</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 804006282091,  So tien goc: 14,</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" t="n">
-        <v>15526087</v>
-      </c>
-      <c r="D131" t="n">
-        <v>-15526087</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>17154000</v>
-      </c>
-      <c r="C132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" t="n">
-        <v>17154000</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>CTY Hoang Huy Phat TT tien don hang Yen To</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" t="n">
-        <v>7842744</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-7842744</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 09/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>0</v>
-      </c>
-      <c r="C134" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 805006288210,  So tien goc: 144</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" t="n">
-        <v>146483382</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-146483382</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Luong T8</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" t="n">
-        <v>46451926</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-46451926</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>man cao dam</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" t="n">
-        <v>43000000</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-43000000</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>bu le</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D138" t="n">
-        <v>-3000000</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">So GD: 500A24907EHG3RKZ Cong Ty Hoang Huy Phat TT </t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" t="n">
-        <v>8250000</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-8250000</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Dot 3</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" t="n">
-        <v>6409728</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-6409728</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>LUONG T8. 2024</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" t="n">
-        <v>49897201</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-49897201</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>lam bu le</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>0</v>
-      </c>
-      <c r="C142" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>LUONG T8.2024</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" t="n">
-        <v>27789564</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-27789564</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>LUONG T8</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" t="n">
-        <v>148635291</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-148635291</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 800006289911,  So tien goc: 53,</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0</v>
-      </c>
-      <c r="C145" t="n">
-        <v>53929068</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-53929068</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>CTY HOANG HUY PHAT TT Tien hang</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
-      <c r="C146" t="n">
-        <v>39656899</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-39656899</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>So GD: 500A2490L9AKRJM0 CTY HOANG HUY PHAT TT tien</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>0</v>
-      </c>
-      <c r="C147" t="n">
-        <v>50615004</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-50615004</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 809006296028,  So tien goc: 130</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
-      <c r="C148" t="n">
-        <v>130539204</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-130539204</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>CT DI:500K2490R7YP040H CTY HOANG HUY PHAT TT PHI Q</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
-      <c r="C149" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 807006299424,  So tien goc: 163</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
-      <c r="C150" t="n">
-        <v>163697863</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-163697863</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>CTY TNHH MTV HOANG HUY PHAT TT tien hang</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" t="n">
-        <v>3153856</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-3153856</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG HOA DON 10560, 11010</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>43353</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-43353</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 09/2024</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>So GD: 500A2490XF4NC425 CTY HOANG HUY PHAT TT tien</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" t="n">
-        <v>278466509</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-278466509</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>UNG LUONG</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>0</v>
-      </c>
-      <c r="C155" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-4000000</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>So GD: 500A24912DUFY5TV CTY Hoang Huy Phat TT tien</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
-      <c r="C156" t="n">
-        <v>285413567</v>
-      </c>
-      <c r="D156" t="n">
-        <v>-285413567</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>dot 3</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
-      <c r="C157" t="n">
-        <v>3204864</v>
-      </c>
-      <c r="D157" t="n">
-        <v>-3204864</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>CTY TNHH HOANG HUY PHAT TT tien hang</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
-      <c r="C158" t="n">
-        <v>261593686</v>
-      </c>
-      <c r="D158" t="n">
-        <v>-261593686</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>So GD: 500A24919B9TKS24 CTY HOANG HUY PHAT TT tien</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
-      <c r="C159" t="n">
-        <v>182998451</v>
-      </c>
-      <c r="D159" t="n">
-        <v>-182998451</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>don hang nuoc suoi</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" t="n">
-        <v>20565160</v>
-      </c>
-      <c r="D160" t="n">
-        <v>-20565160</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>TT tien hang</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
-      <c r="C161" t="n">
-        <v>3182264138</v>
-      </c>
-      <c r="D161" t="n">
-        <v>-3182264138</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH DG GROUP</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>935710</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" t="n">
-        <v>935710</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>So GD: 500A24A00UW5ZTC2 LUAN CHUYEN</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>0</v>
-      </c>
-      <c r="C163" t="n">
-        <v>304000000</v>
-      </c>
-      <c r="D163" t="n">
-        <v>-304000000</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 10/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
-      <c r="C164" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D164" t="n">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>TT tien hang CTY VISSNAN</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>0</v>
-      </c>
-      <c r="C165" t="n">
-        <v>104503478</v>
-      </c>
-      <c r="D165" t="n">
-        <v>-104503478</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>CT DI:500K24A05PHS4HUK LUAN CHUYEN</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
-      <c r="C166" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="D166" t="n">
-        <v>-68000000</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>So GD: 500A24A0A6F0R8AD Cty Hoang huy phat TT tien</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
-      <c r="C167" t="n">
-        <v>249932450</v>
-      </c>
-      <c r="D167" t="n">
-        <v>-249932450</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>chuyen luong</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>0</v>
-      </c>
-      <c r="C168" t="n">
-        <v>714063497</v>
-      </c>
-      <c r="D168" t="n">
-        <v>-714063497</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>luong T9</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>0</v>
-      </c>
-      <c r="C169" t="n">
-        <v>50815147</v>
-      </c>
-      <c r="D169" t="n">
-        <v>-50815147</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>CHUYEN LUONG</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>0</v>
-      </c>
-      <c r="C170" t="n">
-        <v>52472201</v>
-      </c>
-      <c r="D170" t="n">
-        <v>-52472201</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN CẤP THOÁT NƯỚC GIA LAI</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>214950</v>
-      </c>
-      <c r="C171" t="n">
-        <v>0</v>
-      </c>
-      <c r="D171" t="n">
-        <v>214950</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG ( HHB)</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
-      <c r="C172" t="n">
-        <v>25246</v>
-      </c>
-      <c r="D172" t="n">
-        <v>-25246</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CT DI:500K24A0DM5F44SJ CTY HOANG HUY PHAT TT tien </t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" t="n">
-        <v>2055000</v>
-      </c>
-      <c r="D173" t="n">
-        <v>-2055000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Chuyen luong</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" t="n">
-        <v>75745388</v>
-      </c>
-      <c r="D174" t="n">
-        <v>-75745388</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>CT DI:428609239763 PHI QUA TRAM</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0</v>
-      </c>
-      <c r="C175" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D175" t="n">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>chuyen tien tu, ban lam viec</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
-      <c r="C176" t="n">
-        <v>24080000</v>
-      </c>
-      <c r="D176" t="n">
-        <v>-24080000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>So GD: 500A24A0MN61DHEY TT tien hang</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
-      <c r="C177" t="n">
-        <v>164979752</v>
-      </c>
-      <c r="D177" t="n">
-        <v>-164979752</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>So GD: 500A24A0MN5BM0RS TT tien hang</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>0</v>
-      </c>
-      <c r="C178" t="n">
-        <v>45151711</v>
-      </c>
-      <c r="D178" t="n">
-        <v>-45151711</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>ung luong minh tu</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
-      <c r="C179" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D179" t="n">
-        <v>-5000000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 10/2024</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>0</v>
-      </c>
-      <c r="C180" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D180" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>CT DI:429516868246 TT HANG</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
-      <c r="C181" t="n">
-        <v>47752673</v>
-      </c>
-      <c r="D181" t="n">
-        <v>-47752673</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>So GD: 500A24A0Z4JFRETH TT tien hang</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
-      <c r="C182" t="n">
-        <v>169187330</v>
-      </c>
-      <c r="D182" t="n">
-        <v>-169187330</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>CT DI:500K24A164BTPTTT LUAN CHUYEN</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>0</v>
-      </c>
-      <c r="C183" t="n">
-        <v>87000000</v>
-      </c>
-      <c r="D183" t="n">
-        <v>-87000000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>HHP B</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>0</v>
-      </c>
-      <c r="C184" t="n">
-        <v>8110315</v>
-      </c>
-      <c r="D184" t="n">
-        <v>-8110315</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HUY VŨ</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0</v>
-      </c>
-      <c r="D185" t="n">
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>So GD: 500A24A1AVNGN0QK TT tien hang</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>0</v>
-      </c>
-      <c r="C186" t="n">
-        <v>144110327</v>
-      </c>
-      <c r="D186" t="n">
-        <v>-144110327</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>So GD: 500A24A1APG79WQG TT tien hang</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>0</v>
-      </c>
-      <c r="C187" t="n">
-        <v>154942864</v>
-      </c>
-      <c r="D187" t="n">
-        <v>-154942864</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Ma don vi TA0572A</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>0</v>
-      </c>
-      <c r="C188" t="n">
-        <v>29672826</v>
-      </c>
-      <c r="D188" t="n">
-        <v>-29672826</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Ma don vi: TA0572A</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>0</v>
-      </c>
-      <c r="C189" t="n">
-        <v>4807296</v>
-      </c>
-      <c r="D189" t="n">
-        <v>-4807296</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>ma don vi TA0572A</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>0</v>
-      </c>
-      <c r="C190" t="n">
-        <v>3204864</v>
-      </c>
-      <c r="D190" t="n">
-        <v>-3204864</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>TT TIEN HANG HHA</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>0</v>
-      </c>
-      <c r="C191" t="n">
-        <v>47227</v>
-      </c>
-      <c r="D191" t="n">
-        <v>-47227</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 11/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>0</v>
-      </c>
-      <c r="C192" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D192" t="n">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>CT DI:500K24B01PYHCJ0K TIEN BOT QUA TRAM</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
-      <c r="C193" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D193" t="n">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>CT DI:430914549229 TT hang</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
-      <c r="C194" t="n">
-        <v>47593225</v>
-      </c>
-      <c r="D194" t="n">
-        <v>-47593225</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN VIỆT ĐÔNG DƯƠNG</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>24080000</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0</v>
-      </c>
-      <c r="D195" t="n">
-        <v>24080000</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>ung luong</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
-      <c r="C196" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="D196" t="n">
-        <v>-11000000</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>CT TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
-      <c r="C197" t="n">
-        <v>48485</v>
-      </c>
-      <c r="D197" t="n">
-        <v>-48485</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>CT DI:431614793077 thanh toan tien hang</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>0</v>
-      </c>
-      <c r="C198" t="n">
-        <v>48693021</v>
-      </c>
-      <c r="D198" t="n">
-        <v>-48693021</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH BẾN THUYỀN</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>1198000</v>
-      </c>
-      <c r="C199" t="n">
-        <v>0</v>
-      </c>
-      <c r="D199" t="n">
-        <v>1198000</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>So GD: 500A24B0UDNCJ6A9 TT tien hang</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>0</v>
-      </c>
-      <c r="C200" t="n">
-        <v>46113456</v>
-      </c>
-      <c r="D200" t="n">
-        <v>-46113456</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>So GD: 500A24B0U864BN6U TT tien hang</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>0</v>
-      </c>
-      <c r="C201" t="n">
-        <v>248964338</v>
-      </c>
-      <c r="D201" t="n">
-        <v>-248964338</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 11/2024</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
-      <c r="C202" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D202" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>CT DI:500K24B12FA9RLN2 PHI QUA TRAM BOT</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>0</v>
-      </c>
-      <c r="C203" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D203" t="n">
-        <v>-1000000</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>So GD: 500A24B161C5DQKJ TT TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>0</v>
-      </c>
-      <c r="C204" t="n">
-        <v>97040</v>
-      </c>
-      <c r="D204" t="n">
-        <v>-97040</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>So GD: 500A24B15ZY9Y3PH TT TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>0</v>
-      </c>
-      <c r="C205" t="n">
-        <v>35345</v>
-      </c>
-      <c r="D205" t="n">
-        <v>-35345</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>TT Tien hang don 25/11</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>0</v>
-      </c>
-      <c r="C206" t="n">
-        <v>30109778</v>
-      </c>
-      <c r="D206" t="n">
-        <v>-30109778</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>So GD: 500A24B17BGVJ7XC LUAN CHUYEN VCB CTY</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>0</v>
-      </c>
-      <c r="C207" t="n">
-        <v>296000000</v>
-      </c>
-      <c r="D207" t="n">
-        <v>-296000000</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>CT DI:500K24B1CV8ZFA4X LUAN CHUYEN</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>0</v>
-      </c>
-      <c r="C208" t="n">
-        <v>250000000</v>
-      </c>
-      <c r="D208" t="n">
-        <v>-250000000</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Cong Ty Hoang Huy Phat Nop tien Bao hiem T11/2024,</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>0</v>
-      </c>
-      <c r="C209" t="n">
-        <v>3204864</v>
-      </c>
-      <c r="D209" t="n">
-        <v>-3204864</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cong Ty Hoang Huy Phat nop tien Bao hiem T11.2024 </t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>0</v>
-      </c>
-      <c r="C210" t="n">
-        <v>4807296</v>
-      </c>
-      <c r="D210" t="n">
-        <v>-4807296</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>CTY Hoang Huy Phat  Nop tien Bao Hiem T11/2024, Do</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>0</v>
-      </c>
-      <c r="C211" t="n">
-        <v>29606653</v>
-      </c>
-      <c r="D211" t="n">
-        <v>-29606653</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>TT tien nuoc suoi</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>0</v>
-      </c>
-      <c r="C212" t="n">
-        <v>30021640</v>
-      </c>
-      <c r="D212" t="n">
-        <v>-30021640</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 12/2024, So TK: 110649896789, SDT: 09</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>0</v>
-      </c>
-      <c r="C213" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D213" t="n">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TỔNG CÔNG TY THƯƠNG MẠI KỸ THUẬT VÀ ĐẦU TƯ - CÔNG TY CỔ PHẦN TẠI TỈNH GIA LAI</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C214" t="n">
-        <v>0</v>
-      </c>
-      <c r="D214" t="n">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>So GD: 500A24C056JC3J6J Cong Ty TNHH MTV Hoang Huy</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>0</v>
-      </c>
-      <c r="C215" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D215" t="n">
-        <v>-4200000</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>So GD: 500A24C056HWBMJ9 TT tien lop xe</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>0</v>
-      </c>
-      <c r="C216" t="n">
-        <v>4260000</v>
-      </c>
-      <c r="D216" t="n">
-        <v>-4260000</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>CT DI:500K24C0722W14TY PHI QUA TRAM</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>0</v>
-      </c>
-      <c r="C217" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D217" t="n">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>CT DI:434114255477 TT tien hang</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
-      <c r="C218" t="n">
-        <v>53375758</v>
-      </c>
-      <c r="D218" t="n">
-        <v>-53375758</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>DO HOP</t>
-        </is>
-      </c>
-      <c r="B219" t="n">
-        <v>0</v>
-      </c>
-      <c r="C219" t="n">
-        <v>3653000</v>
-      </c>
-      <c r="D219" t="n">
-        <v>-3653000</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>So GD: 500A24C0DV84E0X4 LUAN CHUYEN</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
-      <c r="C220" t="n">
-        <v>515000000</v>
-      </c>
-      <c r="D220" t="n">
-        <v>-515000000</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
-      <c r="C221" t="n">
-        <v>0</v>
-      </c>
-      <c r="D221" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>TT  TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>0</v>
-      </c>
-      <c r="C222" t="n">
-        <v>18420</v>
-      </c>
-      <c r="D222" t="n">
-        <v>-18420</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>So GD: 500A24C0R8DY6PXP TT tien hang</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>0</v>
-      </c>
-      <c r="C223" t="n">
-        <v>103660184</v>
-      </c>
-      <c r="D223" t="n">
-        <v>-103660184</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
         <v>4474840</v>
-      </c>
-      <c r="C224" t="n">
-        <v>0</v>
-      </c>
-      <c r="D224" t="n">
-        <v>4474840</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>15510</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>0</v>
-      </c>
-      <c r="C225" t="n">
-        <v>4474840</v>
-      </c>
-      <c r="D225" t="n">
-        <v>-4474840</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 806006485554,  So tien goc: 104</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>0</v>
-      </c>
-      <c r="C226" t="n">
-        <v>105350819</v>
-      </c>
-      <c r="D226" t="n">
-        <v>-105350819</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 804006499035,  So tien goc: 122</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>0</v>
-      </c>
-      <c r="C227" t="n">
-        <v>123254180</v>
-      </c>
-      <c r="D227" t="n">
-        <v>-123254180</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>CT DI:500K24C0W65DQA24 TT tien giay</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>0</v>
-      </c>
-      <c r="C228" t="n">
-        <v>2055000</v>
-      </c>
-      <c r="D228" t="n">
-        <v>-2055000</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 12/2024</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>0</v>
-      </c>
-      <c r="C229" t="n">
-        <v>35000</v>
-      </c>
-      <c r="D229" t="n">
-        <v>-35000</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>CT DI:500K24C0ZDBC912Z PHI QUA TRAM</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>0</v>
-      </c>
-      <c r="C230" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D230" t="n">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 806006501978,  So tien goc: 121</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>0</v>
-      </c>
-      <c r="C231" t="n">
-        <v>122664949</v>
-      </c>
-      <c r="D231" t="n">
-        <v>-122664949</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 805006523875,  So tien goc: 340</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
-      <c r="C232" t="n">
-        <v>341293114</v>
-      </c>
-      <c r="D232" t="n">
-        <v>-341293114</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 805006525930,  So tien goc: 6,3</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>0</v>
-      </c>
-      <c r="C233" t="n">
-        <v>6377858</v>
-      </c>
-      <c r="D233" t="n">
-        <v>-6377858</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>So GD: 500A24C12FN45B49 TT tien hang</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>0</v>
-      </c>
-      <c r="C234" t="n">
-        <v>194125081</v>
-      </c>
-      <c r="D234" t="n">
-        <v>-194125081</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>TT tien hang HHP B</t>
-        </is>
-      </c>
-      <c r="B235" t="n">
-        <v>0</v>
-      </c>
-      <c r="C235" t="n">
-        <v>403953</v>
-      </c>
-      <c r="D235" t="n">
-        <v>-403953</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>TT tien</t>
-        </is>
-      </c>
-      <c r="B236" t="n">
-        <v>0</v>
-      </c>
-      <c r="C236" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D236" t="n">
-        <v>-70000</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Ma don vi: TA0572A  dot 1</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>0</v>
-      </c>
-      <c r="C237" t="n">
-        <v>28535528</v>
-      </c>
-      <c r="D237" t="n">
-        <v>-28535528</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>DOT 2</t>
-        </is>
-      </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
-      <c r="C238" t="n">
-        <v>4807296</v>
-      </c>
-      <c r="D238" t="n">
-        <v>-4807296</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>`TT TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B239" t="n">
-        <v>0</v>
-      </c>
-      <c r="C239" t="n">
-        <v>26025</v>
-      </c>
-      <c r="D239" t="n">
-        <v>-26025</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>CT DI:436215721465 TT tien hang</t>
-        </is>
-      </c>
-      <c r="B240" t="n">
-        <v>0</v>
-      </c>
-      <c r="C240" t="n">
-        <v>163725251</v>
-      </c>
-      <c r="D240" t="n">
-        <v>-163725251</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 801006508445,  So tien goc: 150</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
-      <c r="C241" t="n">
-        <v>151774784</v>
-      </c>
-      <c r="D241" t="n">
-        <v>-151774784</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 804006514790,  So tien goc: 28,</t>
-        </is>
-      </c>
-      <c r="B242" t="n">
-        <v>0</v>
-      </c>
-      <c r="C242" t="n">
-        <v>31140385</v>
-      </c>
-      <c r="D242" t="n">
-        <v>-31140385</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>So GD: 500A24C1DZFJDHNJ TT TIEN HANG</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>0</v>
-      </c>
-      <c r="C243" t="n">
-        <v>166651447</v>
-      </c>
-      <c r="D243" t="n">
-        <v>-166651447</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Tat toan khoan vay 801006528574,  So tien goc: 169</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>0</v>
-      </c>
-      <c r="C244" t="n">
-        <v>171979824</v>
-      </c>
-      <c r="D244" t="n">
-        <v>-171979824</v>
       </c>
     </row>
   </sheetData>
